--- a/analysis/results/top_price_differences.xlsx
+++ b/analysis/results/top_price_differences.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>brand</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>num_stores</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>min_price</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>max_price</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>price_range</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cv</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>iqr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>price_spread_ratio</t>
         </is>
@@ -471,17 +483,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rogaine Single Pcs</t>
+          <t>Coca Cola</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rogaine</t>
+          <t>Coca Cola</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -491,68 +503,68 @@
         <v>200</v>
       </c>
       <c r="F2" t="n">
-        <v>13320</v>
+        <v>99999</v>
       </c>
       <c r="G2" t="n">
-        <v>13120</v>
+        <v>99799</v>
       </c>
       <c r="H2" t="n">
-        <v>92.33</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>13120</v>
+        <v>99799</v>
       </c>
       <c r="J2" t="n">
-        <v>66.59999999999999</v>
+        <v>499.995</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Guard Super Kernel Sella Basmati Rice 1Kg</t>
+          <t>TASTE OF THE WILD DOG FOOD FOWL GRAIN FREE CANINE 12.2 KG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Taste</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>pet-care</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>414.38</v>
+        <v>2299</v>
       </c>
       <c r="F3" t="n">
-        <v>11849</v>
+        <v>25900</v>
       </c>
       <c r="G3" t="n">
-        <v>11434.62</v>
+        <v>23601</v>
       </c>
       <c r="H3" t="n">
-        <v>87.95999999999999</v>
+        <v>78.03</v>
       </c>
       <c r="I3" t="n">
-        <v>11434.62</v>
+        <v>520</v>
       </c>
       <c r="J3" t="n">
-        <v>28.595</v>
+        <v>11.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jazaa Premium Basmati Rice 1 Kg</t>
+          <t>Red Bull Energy Drink, Sugar Free, 250 ml (24 pack)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jazaa</t>
+          <t>Red Bull</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -567,68 +579,68 @@
         <v>500</v>
       </c>
       <c r="F4" t="n">
-        <v>11299</v>
+        <v>19999</v>
       </c>
       <c r="G4" t="n">
-        <v>10799</v>
+        <v>19499</v>
       </c>
       <c r="H4" t="n">
-        <v>86.53</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>10799</v>
+        <v>13604.25</v>
       </c>
       <c r="J4" t="n">
-        <v>22.598</v>
+        <v>39.998</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2.1 A Fast Charging Universal Travel Adapter</t>
+          <t>FILIPPO BERIO EXTRA VIRGIN OLIVE OIL 5 LTR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>cooking-oil-ghee</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>553</v>
+        <v>3100</v>
       </c>
       <c r="F5" t="n">
-        <v>9399</v>
+        <v>21500</v>
       </c>
       <c r="G5" t="n">
-        <v>8846</v>
+        <v>18400</v>
       </c>
       <c r="H5" t="n">
-        <v>85.27</v>
+        <v>78.67</v>
       </c>
       <c r="I5" t="n">
-        <v>8846</v>
+        <v>18400</v>
       </c>
       <c r="J5" t="n">
-        <v>16.996</v>
+        <v>6.935</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10000mAh Fast Charging Power Bank</t>
+          <t>Guard Easy Cook Sella Rice 1Kg(1 kg)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10000Mah</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -640,592 +652,592 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3902</v>
+        <v>499</v>
       </c>
       <c r="F6" t="n">
-        <v>10799</v>
+        <v>12899</v>
       </c>
       <c r="G6" t="n">
-        <v>6897</v>
+        <v>12400</v>
       </c>
       <c r="H6" t="n">
-        <v>47</v>
+        <v>87.39</v>
       </c>
       <c r="I6" t="n">
-        <v>6897</v>
+        <v>12400</v>
       </c>
       <c r="J6" t="n">
-        <v>2.768</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Falak Select 10 Kg</t>
+          <t>GROOVE DOG FOOD CHICKEN ADULT 1.2KG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Falak</t>
+          <t>Groove</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>meat-poultry</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>3567</v>
+        <v>945</v>
       </c>
       <c r="F7" t="n">
-        <v>9799</v>
+        <v>11999</v>
       </c>
       <c r="G7" t="n">
-        <v>6232</v>
+        <v>11054</v>
       </c>
       <c r="H7" t="n">
-        <v>46.73</v>
+        <v>98.94</v>
       </c>
       <c r="I7" t="n">
-        <v>6232</v>
+        <v>11054</v>
       </c>
       <c r="J7" t="n">
-        <v>2.747</v>
+        <v>12.697</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mcdodo 20W Fast Charger</t>
+          <t>GROOVE DOG FOOD BEEF ADULT 1.2KG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mcdodo</t>
+          <t>Groove</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>meat-poultry</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>945</v>
       </c>
       <c r="F8" t="n">
-        <v>7150</v>
+        <v>11999</v>
       </c>
       <c r="G8" t="n">
-        <v>6101</v>
+        <v>11054</v>
       </c>
       <c r="H8" t="n">
-        <v>72.45</v>
+        <v>125.52</v>
       </c>
       <c r="I8" t="n">
-        <v>6101</v>
+        <v>8324.25</v>
       </c>
       <c r="J8" t="n">
-        <v>6.816</v>
+        <v>12.697</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Chocolate x24</t>
+          <t>Nutella Chocolate Spread</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cakes and Chocolates</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>500</v>
+        <v>2860</v>
       </c>
       <c r="F9" t="n">
-        <v>5160</v>
+        <v>12057</v>
       </c>
       <c r="G9" t="n">
-        <v>4660</v>
+        <v>9197</v>
       </c>
       <c r="H9" t="n">
-        <v>88.02</v>
+        <v>67.83</v>
       </c>
       <c r="I9" t="n">
-        <v>4660</v>
+        <v>9197</v>
       </c>
       <c r="J9" t="n">
-        <v>10.32</v>
+        <v>4.216</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adams Mozzarella Cheese Block 400GM</t>
+          <t>BLACK N DECKER SANDWICH MAKER 2 SLICE TS1000-B5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adams</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>1050</v>
+        <v>5244</v>
       </c>
       <c r="F10" t="n">
-        <v>4999</v>
+        <v>12900</v>
       </c>
       <c r="G10" t="n">
-        <v>3949</v>
+        <v>7656</v>
       </c>
       <c r="H10" t="n">
-        <v>69.79000000000001</v>
+        <v>42.49</v>
       </c>
       <c r="I10" t="n">
-        <v>3949</v>
+        <v>7656</v>
       </c>
       <c r="J10" t="n">
-        <v>4.761</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Strepsils Honey &amp; Lemon 36</t>
+          <t>PANASONIC STEAM IRON NI-U450</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Strepsils</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>tea-coffee</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>8990</v>
       </c>
       <c r="F11" t="n">
-        <v>3895</v>
+        <v>16500</v>
       </c>
       <c r="G11" t="n">
-        <v>3882</v>
+        <v>7510</v>
       </c>
       <c r="H11" t="n">
-        <v>94.3</v>
+        <v>25.56</v>
       </c>
       <c r="I11" t="n">
-        <v>3882</v>
+        <v>6882.5</v>
       </c>
       <c r="J11" t="n">
-        <v>299.615</v>
+        <v>1.835</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rice Basmati 1KG</t>
+          <t>ROYAL CANIN DOG FOOD ADULT X-SMALL 3 KG BASIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Royal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>pet-care</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>466.56</v>
+        <v>9900</v>
       </c>
       <c r="F12" t="n">
-        <v>4345</v>
+        <v>14999</v>
       </c>
       <c r="G12" t="n">
-        <v>3878.44</v>
+        <v>5099</v>
       </c>
       <c r="H12" t="n">
-        <v>95.68000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3845.08</v>
+        <v>3600</v>
       </c>
       <c r="J12" t="n">
-        <v>9.313000000000001</v>
+        <v>1.515</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Adam Pizza Cheese 2 KG</t>
+          <t>Aqua Coco 100% Natural Coconut Water (12pcs of 330ml)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Aqua</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>670</v>
+        <v>565</v>
       </c>
       <c r="F13" t="n">
-        <v>4080</v>
+        <v>5650</v>
       </c>
       <c r="G13" t="n">
-        <v>3410</v>
+        <v>5085</v>
       </c>
       <c r="H13" t="n">
-        <v>76.75</v>
+        <v>80.31</v>
       </c>
       <c r="I13" t="n">
-        <v>3410</v>
+        <v>4183.75</v>
       </c>
       <c r="J13" t="n">
-        <v>6.09</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cadbury Dairy Milk Chocolate Box 38 GM x24</t>
+          <t>MONSTER ENERGY DRINK PUNCH MIXXD 500 ML</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Monster</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cakes and Chocolates</t>
+          <t>beverages</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>250</v>
+        <v>995</v>
       </c>
       <c r="F14" t="n">
-        <v>3480</v>
+        <v>6000</v>
       </c>
       <c r="G14" t="n">
-        <v>3230</v>
+        <v>5005</v>
       </c>
       <c r="H14" t="n">
-        <v>92.56999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3230</v>
+        <v>5005</v>
       </c>
       <c r="J14" t="n">
-        <v>13.92</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nescafe Coffee Gold Blend 50GM</t>
+          <t>CADBURY DAIRY MILK CHOCOLATE BAR THE CLASSIC CREAMY 85 GM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nescafe</t>
+          <t>Cadbury</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Coffee and Whiteners</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1375</v>
+        <v>165</v>
       </c>
       <c r="F15" t="n">
-        <v>4499</v>
+        <v>5160</v>
       </c>
       <c r="G15" t="n">
-        <v>3124</v>
+        <v>4995</v>
       </c>
       <c r="H15" t="n">
-        <v>56.86</v>
+        <v>103.12</v>
       </c>
       <c r="I15" t="n">
-        <v>3124</v>
+        <v>1430</v>
       </c>
       <c r="J15" t="n">
-        <v>3.272</v>
+        <v>31.273</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DAWLANCE WATER DISPENSER 1060</t>
+          <t>TISSUE BOX 92795 G</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dawlance</t>
+          <t>Tissue</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>beverages</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>41900</v>
+        <v>345.51</v>
       </c>
       <c r="F16" t="n">
-        <v>44900</v>
+        <v>4995</v>
       </c>
       <c r="G16" t="n">
-        <v>3000</v>
+        <v>4649.49</v>
       </c>
       <c r="H16" t="n">
-        <v>3.63</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>3000</v>
+        <v>4649.49</v>
       </c>
       <c r="J16" t="n">
-        <v>1.072</v>
+        <v>14.457</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spontex Microfiber Cloth X4</t>
+          <t>MONSTER ENERGY DRINK ULTRA PEACHY KEEN 500 ML</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spontex</t>
+          <t>Monster</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sponges</t>
+          <t>beverages</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>1303</v>
+        <v>995</v>
       </c>
       <c r="F17" t="n">
-        <v>4299</v>
+        <v>5500</v>
       </c>
       <c r="G17" t="n">
-        <v>2996</v>
+        <v>4505</v>
       </c>
       <c r="H17" t="n">
-        <v>57.17</v>
+        <v>86.86</v>
       </c>
       <c r="I17" t="n">
-        <v>2996</v>
+        <v>4505</v>
       </c>
       <c r="J17" t="n">
-        <v>3.299</v>
+        <v>5.528</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deens Cheddar Cheese 2KG</t>
+          <t>Nurpur Full Cream Milk 125 ml (Pack of 24)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deens</t>
+          <t>Nurpur</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>565</v>
+        <v>95</v>
       </c>
       <c r="F18" t="n">
-        <v>3499</v>
+        <v>4440</v>
       </c>
       <c r="G18" t="n">
-        <v>2934</v>
+        <v>4345</v>
       </c>
       <c r="H18" t="n">
-        <v>77.18000000000001</v>
+        <v>96.22</v>
       </c>
       <c r="I18" t="n">
-        <v>2934</v>
+        <v>1940</v>
       </c>
       <c r="J18" t="n">
-        <v>6.193</v>
+        <v>46.737</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tapal Danedar Black Tea 1750GM</t>
+          <t>BLACK &amp; DECKER HAND MIXER M350 BASIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tapal</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>380</v>
+        <v>7665</v>
       </c>
       <c r="F19" t="n">
-        <v>3120</v>
+        <v>11900</v>
       </c>
       <c r="G19" t="n">
-        <v>2740</v>
+        <v>4235</v>
       </c>
       <c r="H19" t="n">
-        <v>83.69</v>
+        <v>22.28</v>
       </c>
       <c r="I19" t="n">
-        <v>2740</v>
+        <v>4235</v>
       </c>
       <c r="J19" t="n">
-        <v>8.211</v>
+        <v>1.553</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Happy Cow Cheese Slices 800 GM</t>
+          <t>Fitlicious Pistachio Berry Nut Bar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>Fitlicious</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>1385</v>
+        <v>210</v>
       </c>
       <c r="F20" t="n">
-        <v>4075</v>
+        <v>3645</v>
       </c>
       <c r="G20" t="n">
-        <v>2690</v>
+        <v>3435</v>
       </c>
       <c r="H20" t="n">
-        <v>52.67</v>
+        <v>130.55</v>
       </c>
       <c r="I20" t="n">
-        <v>2690</v>
+        <v>2576.25</v>
       </c>
       <c r="J20" t="n">
-        <v>2.942</v>
+        <v>17.357</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Delmonte Pineapple Tidbits 567 GM</t>
+          <t>WHISKAS CAT FOOD JELLY MIX SELECTION 7+YEAR 85 GM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Delmonte</t>
+          <t>Whiskas</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Canned Fruits</t>
+          <t>pet-care</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>590</v>
+        <v>265</v>
       </c>
       <c r="F21" t="n">
-        <v>3250</v>
+        <v>3699</v>
       </c>
       <c r="G21" t="n">
-        <v>2660</v>
+        <v>3434</v>
       </c>
       <c r="H21" t="n">
-        <v>77.11</v>
+        <v>68.23</v>
       </c>
       <c r="I21" t="n">
-        <v>2660</v>
+        <v>3334</v>
       </c>
       <c r="J21" t="n">
-        <v>5.508</v>
+        <v>13.958</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/results/top_price_differences.xlsx
+++ b/analysis/results/top_price_differences.xlsx
@@ -521,126 +521,126 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TASTE OF THE WILD DOG FOOD FOWL GRAIN FREE CANINE 12.2 KG</t>
+          <t>BALLMAN PARIS WALLET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taste</t>
+          <t>Ballman</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>pet-care</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>2299</v>
+        <v>180</v>
       </c>
       <c r="F3" t="n">
-        <v>25900</v>
+        <v>60000</v>
       </c>
       <c r="G3" t="n">
-        <v>23601</v>
+        <v>59820</v>
       </c>
       <c r="H3" t="n">
-        <v>78.03</v>
+        <v>82.41</v>
       </c>
       <c r="I3" t="n">
-        <v>520</v>
+        <v>59820</v>
       </c>
       <c r="J3" t="n">
-        <v>11.266</v>
+        <v>333.333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Red Bull Energy Drink, Sugar Free, 250 ml (24 pack)</t>
+          <t>HONEY DISPENSER AA18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Red Bull</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>500</v>
+        <v>745</v>
       </c>
       <c r="F4" t="n">
-        <v>19999</v>
+        <v>39501</v>
       </c>
       <c r="G4" t="n">
-        <v>19499</v>
+        <v>38756</v>
       </c>
       <c r="H4" t="n">
-        <v>85.90000000000001</v>
+        <v>113.67</v>
       </c>
       <c r="I4" t="n">
-        <v>13604.25</v>
+        <v>38756</v>
       </c>
       <c r="J4" t="n">
-        <v>39.998</v>
+        <v>53.021</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>FILIPPO BERIO EXTRA VIRGIN OLIVE OIL 5 LTR</t>
+          <t>CLARINS FACE EF DAY CR DS 50ML 2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Filippo</t>
+          <t>Clarins</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cooking-oil-ghee</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>3100</v>
+        <v>3500</v>
       </c>
       <c r="F5" t="n">
-        <v>21500</v>
+        <v>29750</v>
       </c>
       <c r="G5" t="n">
-        <v>18400</v>
+        <v>26250</v>
       </c>
       <c r="H5" t="n">
-        <v>78.67</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>18400</v>
+        <v>26175</v>
       </c>
       <c r="J5" t="n">
-        <v>6.935</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Guard Easy Cook Sella Rice 1Kg(1 kg)</t>
+          <t>AUDIONIC EARBUDS BATTLEBUDS PRO GREEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Audionic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -652,592 +652,592 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>499</v>
+        <v>3899</v>
       </c>
       <c r="F6" t="n">
-        <v>12899</v>
+        <v>28900</v>
       </c>
       <c r="G6" t="n">
-        <v>12400</v>
+        <v>25001</v>
       </c>
       <c r="H6" t="n">
-        <v>87.39</v>
+        <v>87.78</v>
       </c>
       <c r="I6" t="n">
-        <v>12400</v>
+        <v>25001</v>
       </c>
       <c r="J6" t="n">
-        <v>25.85</v>
+        <v>7.412</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GROOVE DOG FOOD CHICKEN ADULT 1.2KG</t>
+          <t>TASTE OF THE WILD DOG FOOD FOWL GRAIN FREE CANINE 12.2 KG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Groove</t>
+          <t>Taste</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>meat-poultry</t>
+          <t>pet-care</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>945</v>
+        <v>2299</v>
       </c>
       <c r="F7" t="n">
-        <v>11999</v>
+        <v>25900</v>
       </c>
       <c r="G7" t="n">
-        <v>11054</v>
+        <v>23601</v>
       </c>
       <c r="H7" t="n">
-        <v>98.94</v>
+        <v>78.03</v>
       </c>
       <c r="I7" t="n">
-        <v>11054</v>
+        <v>520</v>
       </c>
       <c r="J7" t="n">
-        <v>12.697</v>
+        <v>11.266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GROOVE DOG FOOD BEEF ADULT 1.2KG</t>
+          <t>Red Bull Energy Drink, Sugar Free, 250 ml (24 pack)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Groove</t>
+          <t>Red Bull</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>meat-poultry</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>945</v>
+        <v>500</v>
       </c>
       <c r="F8" t="n">
-        <v>11999</v>
+        <v>19999</v>
       </c>
       <c r="G8" t="n">
-        <v>11054</v>
+        <v>19499</v>
       </c>
       <c r="H8" t="n">
-        <v>125.52</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>8324.25</v>
+        <v>13604.25</v>
       </c>
       <c r="J8" t="n">
-        <v>12.697</v>
+        <v>39.998</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nutella Chocolate Spread</t>
+          <t>FILIPPO BERIO EXTRA VIRGIN OLIVE OIL 5 LTR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nutella</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>cooking-oil-ghee</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>2860</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="n">
-        <v>12057</v>
+        <v>21500</v>
       </c>
       <c r="G9" t="n">
-        <v>9197</v>
+        <v>18400</v>
       </c>
       <c r="H9" t="n">
-        <v>67.83</v>
+        <v>78.67</v>
       </c>
       <c r="I9" t="n">
-        <v>9197</v>
+        <v>18400</v>
       </c>
       <c r="J9" t="n">
-        <v>4.216</v>
+        <v>6.935</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BLACK N DECKER SANDWICH MAKER 2 SLICE TS1000-B5</t>
+          <t>Monin Strawberry Fruit Puree</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Monin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>5244</v>
+        <v>108</v>
       </c>
       <c r="F10" t="n">
-        <v>12900</v>
+        <v>12880</v>
       </c>
       <c r="G10" t="n">
-        <v>7656</v>
+        <v>12772</v>
       </c>
       <c r="H10" t="n">
-        <v>42.49</v>
+        <v>61</v>
       </c>
       <c r="I10" t="n">
-        <v>7656</v>
+        <v>5113</v>
       </c>
       <c r="J10" t="n">
-        <v>2.46</v>
+        <v>119.259</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PANASONIC STEAM IRON NI-U450</t>
+          <t>Guard Easy Cook Sella Rice 1Kg(1 kg)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>Guard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tea-coffee</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>8990</v>
+        <v>499</v>
       </c>
       <c r="F11" t="n">
-        <v>16500</v>
+        <v>12899</v>
       </c>
       <c r="G11" t="n">
-        <v>7510</v>
+        <v>12400</v>
       </c>
       <c r="H11" t="n">
-        <v>25.56</v>
+        <v>87.39</v>
       </c>
       <c r="I11" t="n">
-        <v>6882.5</v>
+        <v>12400</v>
       </c>
       <c r="J11" t="n">
-        <v>1.835</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ROYAL CANIN DOG FOOD ADULT X-SMALL 3 KG BASIC</t>
+          <t>BABY WALKER IR SH916</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Royal</t>
+          <t>Baby</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pet-care</t>
+          <t>baby-care</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>9900</v>
+        <v>1999</v>
       </c>
       <c r="F12" t="n">
-        <v>14999</v>
+        <v>13900</v>
       </c>
       <c r="G12" t="n">
-        <v>5099</v>
+        <v>11901</v>
       </c>
       <c r="H12" t="n">
-        <v>18.6</v>
+        <v>83.23</v>
       </c>
       <c r="I12" t="n">
-        <v>3600</v>
+        <v>11851</v>
       </c>
       <c r="J12" t="n">
-        <v>1.515</v>
+        <v>6.953</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aqua Coco 100% Natural Coconut Water (12pcs of 330ml)</t>
+          <t>KIT KAT DOUBLE CHOCOLATE BAR 100G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aqua</t>
+          <t>Kit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>chocolates</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>565</v>
+        <v>1395</v>
       </c>
       <c r="F13" t="n">
-        <v>5650</v>
+        <v>12600</v>
       </c>
       <c r="G13" t="n">
-        <v>5085</v>
+        <v>11205</v>
       </c>
       <c r="H13" t="n">
-        <v>80.31</v>
+        <v>103.61</v>
       </c>
       <c r="I13" t="n">
-        <v>4183.75</v>
+        <v>11205</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>9.032</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MONSTER ENERGY DRINK PUNCH MIXXD 500 ML</t>
+          <t>GROOVE DOG FOOD CHICKEN ADULT 1.2KG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Monster</t>
+          <t>Groove</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>beverages</t>
+          <t>meat-poultry</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>995</v>
+        <v>945</v>
       </c>
       <c r="F14" t="n">
-        <v>6000</v>
+        <v>11999</v>
       </c>
       <c r="G14" t="n">
-        <v>5005</v>
+        <v>11054</v>
       </c>
       <c r="H14" t="n">
-        <v>90.2</v>
+        <v>98.94</v>
       </c>
       <c r="I14" t="n">
-        <v>5005</v>
+        <v>11054</v>
       </c>
       <c r="J14" t="n">
-        <v>6.03</v>
+        <v>12.697</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CADBURY DAIRY MILK CHOCOLATE BAR THE CLASSIC CREAMY 85 GM</t>
+          <t>GROOVE DOG FOOD BEEF ADULT 1.2KG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cadbury</t>
+          <t>Groove</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>meat-poultry</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>165</v>
+        <v>945</v>
       </c>
       <c r="F15" t="n">
-        <v>5160</v>
+        <v>11999</v>
       </c>
       <c r="G15" t="n">
-        <v>4995</v>
+        <v>11054</v>
       </c>
       <c r="H15" t="n">
-        <v>103.12</v>
+        <v>125.52</v>
       </c>
       <c r="I15" t="n">
-        <v>1430</v>
+        <v>8324.25</v>
       </c>
       <c r="J15" t="n">
-        <v>31.273</v>
+        <v>12.697</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TISSUE BOX 92795 G</t>
+          <t>Nutella Chocolate Spread</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tissue</t>
+          <t>Nutella</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>345.51</v>
+        <v>2860</v>
       </c>
       <c r="F16" t="n">
-        <v>4995</v>
+        <v>12057</v>
       </c>
       <c r="G16" t="n">
-        <v>4649.49</v>
+        <v>9197</v>
       </c>
       <c r="H16" t="n">
-        <v>74.01000000000001</v>
+        <v>67.83</v>
       </c>
       <c r="I16" t="n">
-        <v>4649.49</v>
+        <v>9197</v>
       </c>
       <c r="J16" t="n">
-        <v>14.457</v>
+        <v>4.216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MONSTER ENERGY DRINK ULTRA PEACHY KEEN 500 ML</t>
+          <t>Alfatah Extra Long Gran New Steam Rice 25kg</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Monster</t>
+          <t>Alfatah</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>beverages</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>995</v>
+        <v>1528</v>
       </c>
       <c r="F17" t="n">
-        <v>5500</v>
+        <v>10500</v>
       </c>
       <c r="G17" t="n">
-        <v>4505</v>
+        <v>8972</v>
       </c>
       <c r="H17" t="n">
-        <v>86.86</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>4505</v>
+        <v>8972</v>
       </c>
       <c r="J17" t="n">
-        <v>5.528</v>
+        <v>6.872</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nurpur Full Cream Milk 125 ml (Pack of 24)</t>
+          <t>DINNER SET 72PC MARBLE HZDW4428 KC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nurpur</t>
+          <t>Dinner</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>30010</v>
       </c>
       <c r="F18" t="n">
-        <v>4440</v>
+        <v>38900</v>
       </c>
       <c r="G18" t="n">
-        <v>4345</v>
+        <v>8890</v>
       </c>
       <c r="H18" t="n">
-        <v>96.22</v>
+        <v>13.41</v>
       </c>
       <c r="I18" t="n">
-        <v>1940</v>
+        <v>8890</v>
       </c>
       <c r="J18" t="n">
-        <v>46.737</v>
+        <v>1.296</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BLACK &amp; DECKER HAND MIXER M350 BASIC</t>
+          <t>NEUTROGENA BODY OIL 250ML</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Neutrogena</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>general</t>
+          <t>cooking-oil-ghee</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>7665</v>
+        <v>380</v>
       </c>
       <c r="F19" t="n">
-        <v>11900</v>
+        <v>8900</v>
       </c>
       <c r="G19" t="n">
-        <v>4235</v>
+        <v>8520</v>
       </c>
       <c r="H19" t="n">
-        <v>22.28</v>
+        <v>104.5</v>
       </c>
       <c r="I19" t="n">
-        <v>4235</v>
+        <v>8515</v>
       </c>
       <c r="J19" t="n">
-        <v>1.553</v>
+        <v>23.421</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Fitlicious Pistachio Berry Nut Bar</t>
+          <t>BLACK N DECKER SANDWICH MAKER 2 SLICE TS1000-B5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fitlicious</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Products</t>
+          <t>general</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>5244</v>
       </c>
       <c r="F20" t="n">
-        <v>3645</v>
+        <v>12900</v>
       </c>
       <c r="G20" t="n">
-        <v>3435</v>
+        <v>7656</v>
       </c>
       <c r="H20" t="n">
-        <v>130.55</v>
+        <v>42.49</v>
       </c>
       <c r="I20" t="n">
-        <v>2576.25</v>
+        <v>7656</v>
       </c>
       <c r="J20" t="n">
-        <v>17.357</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WHISKAS CAT FOOD JELLY MIX SELECTION 7+YEAR 85 GM</t>
+          <t>PANASONIC STEAM IRON NI-U450</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Whiskas</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>pet-care</t>
+          <t>tea-coffee</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>265</v>
+        <v>8990</v>
       </c>
       <c r="F21" t="n">
-        <v>3699</v>
+        <v>16500</v>
       </c>
       <c r="G21" t="n">
-        <v>3434</v>
+        <v>7510</v>
       </c>
       <c r="H21" t="n">
-        <v>68.23</v>
+        <v>25.56</v>
       </c>
       <c r="I21" t="n">
-        <v>3334</v>
+        <v>6882.5</v>
       </c>
       <c r="J21" t="n">
-        <v>13.958</v>
+        <v>1.835</v>
       </c>
     </row>
   </sheetData>
